--- a/Tables/pairwise_adonis_same_sheet_Nov.xlsx
+++ b/Tables/pairwise_adonis_same_sheet_Nov.xlsx
@@ -467,10 +467,10 @@
         <v>2.41114147493382</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0597</v>
+        <v>0.0605</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3582</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="3">
@@ -505,10 +505,10 @@
         <v>2.52107861282322</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0816</v>
+        <v>0.0779</v>
       </c>
       <c r="L3" t="n">
-        <v>0.408</v>
+        <v>0.3895</v>
       </c>
     </row>
     <row r="4">
@@ -543,7 +543,7 @@
         <v>0.381383618273158</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7867</v>
+        <v>0.7935</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -581,7 +581,7 @@
         <v>0.584709190687182</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6692</v>
+        <v>0.674</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -619,10 +619,10 @@
         <v>1.509383389883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2057</v>
+        <v>0.2087</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6388</v>
+        <v>0.6596</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         <v>1.65996617475719</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1597</v>
+        <v>0.1649</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6388</v>
+        <v>0.6596</v>
       </c>
     </row>
   </sheetData>
